--- a/data/business_data.xlsx.xlsx
+++ b/data/business_data.xlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -64,6 +64,9 @@
   <si>
     <t>Rent</t>
   </si>
+  <si>
+    <t>Calculator</t>
+  </si>
 </sst>
 </file>
 
@@ -98,8 +101,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -411,16 +415,16 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46027</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2">
@@ -429,16 +433,16 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46058</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>20</v>
       </c>
       <c r="E3">
@@ -447,9 +451,21 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -13043,24 +13059,24 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46027</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46058</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>1000</v>
       </c>
     </row>
@@ -13083,7 +13099,7 @@
       </c>
       <c r="B1">
         <f>SUM(Sales!E:E)</f>
-        <v>300</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -13101,7 +13117,7 @@
       </c>
       <c r="B3">
         <f xml:space="preserve"> B1 - B2</f>
-        <v>-900</v>
+        <v>6100</v>
       </c>
     </row>
   </sheetData>
